--- a/torneio_interno_planilha_preenchivel.xlsx
+++ b/torneio_interno_planilha_preenchivel.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F87284B-8867-47ED-AA31-B0A35E0E9F3B}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bb6a416c133d750/Documentos/Projects/Camp_Volei/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A81809DB-4CE9-43B4-A37D-FC3FFC16CC66}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela de Jogos" sheetId="1" r:id="rId1"/>
-    <sheet name="Classificação" sheetId="2" r:id="rId2"/>
+    <sheet name="Time" sheetId="3" r:id="rId2"/>
+    <sheet name="Classificação" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabela de Jogos'!$A$3:$G$13</definedName>
@@ -57,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
   <si>
     <t>Torneio Interno – Planilha de Jogos</t>
   </si>
@@ -150,6 +156,120 @@
   </si>
   <si>
     <t>Saldo</t>
+  </si>
+  <si>
+    <t>Grazi</t>
+  </si>
+  <si>
+    <t>Stella</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>Neidoka</t>
+  </si>
+  <si>
+    <t>Bianca</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>Eliane</t>
+  </si>
+  <si>
+    <t>Milena</t>
+  </si>
+  <si>
+    <t>Camila M.</t>
+  </si>
+  <si>
+    <t>Erica</t>
+  </si>
+  <si>
+    <t>Ednéia</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>Debora</t>
+  </si>
+  <si>
+    <t>Katia</t>
+  </si>
+  <si>
+    <t>Janaina</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>Zuleide</t>
+  </si>
+  <si>
+    <t>Marina</t>
+  </si>
+  <si>
+    <t>Fabiana</t>
+  </si>
+  <si>
+    <t>Sirlene</t>
+  </si>
+  <si>
+    <t>Fabiana S.</t>
+  </si>
+  <si>
+    <t>Michele</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>Ieda</t>
+  </si>
+  <si>
+    <t>Gracielle</t>
+  </si>
+  <si>
+    <t>Irene</t>
+  </si>
+  <si>
+    <t>Gizele</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>Helena</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>Cristiane</t>
+  </si>
+  <si>
+    <t>Gazielle</t>
+  </si>
+  <si>
+    <t>Luciane</t>
+  </si>
+  <si>
+    <t>T / R</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
 </sst>
 </file>
@@ -157,9 +277,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="d/m/yy;@"/>
+    <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -276,13 +396,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -295,15 +420,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -319,6 +436,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -606,10 +727,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -618,30 +739,25 @@
     <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT('Tabela de Jogos'!$G$4:$G$13='Tabela de Jogos'!A4B2)</f>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2" t="e" cm="1">
+        <f t="array" ref="D2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT('Tabela de Jogos'!$G$4:$G$13='Tabela de Jogos'!A4B2)</f>
         <v>#NAME?</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A3" s="18" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -663,8 +779,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A4" s="19">
+    <row r="4" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
         <v>46248</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -686,8 +802,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A5" s="19">
+    <row r="5" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
         <v>46248</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -709,8 +825,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A6" s="19">
+    <row r="6" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>46255</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -732,8 +848,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A7" s="19">
+    <row r="7" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
         <v>46255</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -755,8 +871,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A8" s="19">
+    <row r="8" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>46262</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -778,8 +894,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A9" s="19">
+    <row r="9" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
         <v>46262</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -801,8 +917,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A10" s="19">
+    <row r="10" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
         <v>46276</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -820,8 +936,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A11" s="19">
+    <row r="11" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
         <v>46276</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -839,8 +955,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A12" s="19">
+    <row r="12" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
         <v>46283</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -858,8 +974,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A13" s="19">
+    <row r="13" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
         <v>46283</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -877,19 +993,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A15" s="19">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
         <v>46290</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -909,8 +1025,8 @@
         <v>Onça</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A16" s="19">
+    <row r="16" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
         <v>46290</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -930,20 +1046,19 @@
         <v>Dálmata</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A18" s="19">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
         <v>46297</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -960,32 +1075,29 @@
       <c r="G18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A19" s="19"/>
+    </row>
+    <row r="19" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A20" s="11" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A21" s="19">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
         <v>46297</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1002,187 +1114,21 @@
       <c r="G21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="B29" s="6"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="6"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="6"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="6"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1197,21 +1143,227 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F36AF8F-2E55-445B-B4FF-29554B5B33C8}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -1239,12 +1391,8 @@
       <c r="I1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1280,12 +1428,8 @@
         <f>G2-H2</f>
         <v>2</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1320,12 +1464,8 @@
         <f t="shared" ref="I3:I6" si="0">G3-H3</f>
         <v>-2</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1360,12 +1500,8 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1400,12 +1536,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1440,42 +1572,8 @@
         <f t="shared" si="0"/>
         <v>-7</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -1503,206 +1601,153 @@
       <c r="I9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="str" cm="1">
+      <c r="B10" s="7" t="str" cm="1">
         <f t="array" ref="B10:I14">_xlfn.SORTBY(B2:I6,F2:F6,-1)</f>
         <v>Girafa</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <v>3</v>
       </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="D10" s="7">
+        <v>2</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7">
         <v>6</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="7">
         <v>6</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="7">
         <v>3</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <v>3</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" spans="1:13">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2</v>
       </c>
-      <c r="B11" s="9" t="str">
+      <c r="B11" s="7" t="str">
         <v>Tigre</v>
       </c>
-      <c r="C11" s="9">
-        <v>2</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="7">
+        <v>2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7">
         <v>0</v>
       </c>
-      <c r="F11" s="9">
-        <v>5</v>
-      </c>
-      <c r="G11" s="9">
-        <v>5</v>
-      </c>
-      <c r="H11" s="9">
-        <v>1</v>
-      </c>
-      <c r="I11" s="9">
+      <c r="F11" s="7">
+        <v>5</v>
+      </c>
+      <c r="G11" s="7">
+        <v>5</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7">
         <v>4</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:13">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>3</v>
       </c>
-      <c r="B12" s="9" t="str">
+      <c r="B12" s="7" t="str">
         <v>Dálmata</v>
       </c>
-      <c r="C12" s="9">
-        <v>2</v>
-      </c>
-      <c r="D12" s="9">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="C12" s="7">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
         <v>4</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="7">
         <v>4</v>
       </c>
-      <c r="H12" s="9">
-        <v>2</v>
-      </c>
-      <c r="I12" s="9">
-        <v>2</v>
-      </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="H12" s="7">
+        <v>2</v>
+      </c>
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>4</v>
       </c>
-      <c r="B13" s="9" t="str">
+      <c r="B13" s="7" t="str">
         <v>Onça</v>
       </c>
-      <c r="C13" s="9">
-        <v>2</v>
-      </c>
-      <c r="D13" s="9">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9">
-        <v>2</v>
-      </c>
-      <c r="G13" s="9">
-        <v>2</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7">
         <v>4</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="7">
         <v>-2</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>5</v>
       </c>
-      <c r="B14" s="9" t="str">
+      <c r="B14" s="7" t="str">
         <v>Zebra</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <v>3</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>0</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <v>3</v>
       </c>
-      <c r="F14" s="9">
-        <v>1</v>
-      </c>
-      <c r="G14" s="9">
-        <v>1</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7">
         <v>8</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <v>-7</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/torneio_interno_planilha_preenchivel.xlsx
+++ b/torneio_interno_planilha_preenchivel.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bb6a416c133d750/Documentos/Projects/Camp_Volei/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A81809DB-4CE9-43B4-A37D-FC3FFC16CC66}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DD0F04A-6414-2743-A588-866E94E643E4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela de Jogos" sheetId="1" r:id="rId1"/>
-    <sheet name="Time" sheetId="3" r:id="rId2"/>
-    <sheet name="Classificação" sheetId="2" r:id="rId3"/>
+    <sheet name="Classificação" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabela de Jogos'!$A$3:$G$13</definedName>
@@ -63,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
   <si>
     <t>Torneio Interno – Planilha de Jogos</t>
   </si>
@@ -156,120 +150,6 @@
   </si>
   <si>
     <t>Saldo</t>
-  </si>
-  <si>
-    <t>Grazi</t>
-  </si>
-  <si>
-    <t>Stella</t>
-  </si>
-  <si>
-    <t>Julia</t>
-  </si>
-  <si>
-    <t>Neidoka</t>
-  </si>
-  <si>
-    <t>Bianca</t>
-  </si>
-  <si>
-    <t>Vanessa</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Eliane</t>
-  </si>
-  <si>
-    <t>Milena</t>
-  </si>
-  <si>
-    <t>Camila M.</t>
-  </si>
-  <si>
-    <t>Erica</t>
-  </si>
-  <si>
-    <t>Ednéia</t>
-  </si>
-  <si>
-    <t>Valeria</t>
-  </si>
-  <si>
-    <t>Tania</t>
-  </si>
-  <si>
-    <t>Debora</t>
-  </si>
-  <si>
-    <t>Katia</t>
-  </si>
-  <si>
-    <t>Janaina</t>
-  </si>
-  <si>
-    <t>Fernanda</t>
-  </si>
-  <si>
-    <t>Zuleide</t>
-  </si>
-  <si>
-    <t>Marina</t>
-  </si>
-  <si>
-    <t>Fabiana</t>
-  </si>
-  <si>
-    <t>Sirlene</t>
-  </si>
-  <si>
-    <t>Fabiana S.</t>
-  </si>
-  <si>
-    <t>Michele</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>Ieda</t>
-  </si>
-  <si>
-    <t>Gracielle</t>
-  </si>
-  <si>
-    <t>Irene</t>
-  </si>
-  <si>
-    <t>Gizele</t>
-  </si>
-  <si>
-    <t>Carolina</t>
-  </si>
-  <si>
-    <t>Helena</t>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>Cristiane</t>
-  </si>
-  <si>
-    <t>Gazielle</t>
-  </si>
-  <si>
-    <t>Luciane</t>
-  </si>
-  <si>
-    <t>T / R</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>R</t>
   </si>
 </sst>
 </file>
@@ -379,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -396,11 +276,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -420,7 +303,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,10 +319,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -727,37 +606,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="33.2265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.97265625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11.97265625" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" customWidth="1"/>
+    <col min="6" max="6" width="11.97265625" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D2" t="e" cm="1">
-        <f t="array" ref="D2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT('Tabela de Jogos'!$G$4:$G$13='Tabela de Jogos'!A4B2)</f>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT('Tabela de Jogos'!$G$4:$G$13='Tabela de Jogos'!A4B2)</f>
         <v>#NAME?</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -779,8 +663,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+    <row r="4" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14">
         <v>46248</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -802,8 +686,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+    <row r="5" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
         <v>46248</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -825,8 +709,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+    <row r="6" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14">
         <v>46255</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -848,8 +732,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+    <row r="7" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14">
         <v>46255</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -871,8 +755,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
+    <row r="8" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14">
         <v>46262</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -894,8 +778,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
+    <row r="9" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14">
         <v>46262</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -917,8 +801,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
+    <row r="10" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
         <v>46276</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -927,17 +811,21 @@
       <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
       <c r="G10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+    <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="14">
         <v>46276</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -955,8 +843,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
+    <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="14">
         <v>46283</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -974,8 +862,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
+    <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="14">
         <v>46283</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -993,19 +881,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="14">
         <v>46290</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1013,7 +901,7 @@
       </c>
       <c r="C15" s="2" t="str">
         <f>Classificação!B10</f>
-        <v>Girafa</v>
+        <v>Dálmata</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
@@ -1025,8 +913,8 @@
         <v>Onça</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
+    <row r="16" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14">
         <v>46290</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1034,7 +922,7 @@
       </c>
       <c r="C16" s="2" t="str">
         <f>Classificação!B11</f>
-        <v>Tigre</v>
+        <v>Girafa</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2" t="s">
@@ -1043,22 +931,23 @@
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="str">
         <f>Classificação!B12</f>
-        <v>Dálmata</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+        <v>Tigre</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="14">
         <v>46297</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1075,29 +964,32 @@
       <c r="G18" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="14"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:7" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="14">
         <v>46297</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1114,21 +1006,187 @@
       <c r="G21" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="6"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="6"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="6"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39" s="6"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41" s="6"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="6"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="6"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="6"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1143,227 +1201,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F36AF8F-2E55-445B-B4FF-29554B5B33C8}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="1" max="1" width="7.93359375" customWidth="1"/>
+    <col min="2" max="2" width="18.0234375" customWidth="1"/>
+    <col min="3" max="3" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.12890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" customWidth="1"/>
+    <col min="6" max="7" width="11.97265625" customWidth="1"/>
+    <col min="8" max="8" width="13.98828125" customWidth="1"/>
+    <col min="9" max="9" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -1391,8 +1243,12 @@
       <c r="I1" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1406,7 +1262,7 @@
       </c>
       <c r="D2" s="5" cm="1">
         <f t="array" ref="D2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="5" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1414,22 +1270,26 @@
       </c>
       <c r="F2" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B2,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B2,'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" s="5" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" s="5" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="5">
         <f>G2-H2</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1438,7 +1298,7 @@
       </c>
       <c r="C3" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B3,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B3,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="5" cm="1">
         <f t="array" ref="D3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1446,26 +1306,30 @@
       </c>
       <c r="E3" s="5" cm="1">
         <f t="array" ref="E3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B3,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B3,'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="5" cm="1">
         <f t="array" ref="G3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="5" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I6" si="0">G3-H3</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>-3</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1474,7 +1338,7 @@
       </c>
       <c r="C4" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B4,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B4,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" ref="D4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1500,8 +1364,12 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1536,8 +1404,12 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1572,8 +1444,42 @@
         <f t="shared" si="0"/>
         <v>-7</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -1601,153 +1507,206 @@
       <c r="I9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="str" cm="1">
+      <c r="B10" s="11" t="str" cm="1">
         <f t="array" ref="B10:I14">_xlfn.SORTBY(B2:I6,F2:F6,-1)</f>
-        <v>Girafa</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7">
+        <v>Dálmata</v>
+      </c>
+      <c r="C10" s="9">
         <v>2</v>
       </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="D10" s="9">
+        <v>2</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9">
         <v>6</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="9">
         <v>6</v>
       </c>
-      <c r="H10" s="7">
-        <v>3</v>
-      </c>
-      <c r="I10" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H10" s="9">
+        <v>3</v>
+      </c>
+      <c r="I10" s="9">
+        <v>3</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>2</v>
       </c>
-      <c r="B11" s="7" t="str">
+      <c r="B11" s="9" t="str">
+        <v>Girafa</v>
+      </c>
+      <c r="C11" s="9">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9">
+        <v>6</v>
+      </c>
+      <c r="G11" s="9">
+        <v>6</v>
+      </c>
+      <c r="H11" s="9">
+        <v>3</v>
+      </c>
+      <c r="I11" s="9">
+        <v>3</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>3</v>
+      </c>
+      <c r="B12" s="9" t="str">
         <v>Tigre</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C12" s="9">
+        <v>3</v>
+      </c>
+      <c r="D12" s="9">
         <v>2</v>
       </c>
-      <c r="D11" s="7">
-        <v>2</v>
-      </c>
-      <c r="E11" s="7">
+      <c r="E12" s="9">
         <v>0</v>
       </c>
-      <c r="F11" s="7">
-        <v>5</v>
-      </c>
-      <c r="G11" s="7">
-        <v>5</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1</v>
-      </c>
-      <c r="I11" s="7">
+      <c r="F12" s="9">
+        <v>5</v>
+      </c>
+      <c r="G12" s="9">
+        <v>5</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <v>3</v>
-      </c>
-      <c r="B12" s="7" t="str">
-        <v>Dálmata</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7">
-        <v>4</v>
-      </c>
-      <c r="G12" s="7">
-        <v>4</v>
-      </c>
-      <c r="H12" s="7">
-        <v>2</v>
-      </c>
-      <c r="I12" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>4</v>
       </c>
-      <c r="B13" s="7" t="str">
+      <c r="B13" s="9" t="str">
         <v>Onça</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="9">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9">
         <v>2</v>
       </c>
-      <c r="D13" s="7">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7">
-        <v>2</v>
-      </c>
-      <c r="G13" s="7">
-        <v>2</v>
-      </c>
-      <c r="H13" s="7">
-        <v>4</v>
-      </c>
-      <c r="I13" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F13" s="9">
+        <v>3</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <v>6</v>
+      </c>
+      <c r="I13" s="9">
+        <v>-3</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>5</v>
       </c>
-      <c r="B14" s="7" t="str">
+      <c r="B14" s="9" t="str">
         <v>Zebra</v>
       </c>
-      <c r="C14" s="7">
-        <v>3</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="9">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9">
         <v>0</v>
       </c>
-      <c r="E14" s="7">
-        <v>3</v>
-      </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="E14" s="9">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1</v>
+      </c>
+      <c r="G14" s="9">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9">
         <v>8</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="9">
         <v>-7</v>
       </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/torneio_interno_planilha_preenchivel.xlsx
+++ b/torneio_interno_planilha_preenchivel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="138" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DD0F04A-6414-2743-A588-866E94E643E4}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B81C87A7-5C75-6446-B183-21C9322E59B3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>Torneio Interno – Planilha de Jogos</t>
   </si>
@@ -150,6 +150,18 @@
   </si>
   <si>
     <t>Saldo</t>
+  </si>
+  <si>
+    <t>1° Lugar</t>
+  </si>
+  <si>
+    <t>2° Lugar</t>
+  </si>
+  <si>
+    <t>4° Lugar</t>
+  </si>
+  <si>
+    <t>3° Lugar</t>
   </si>
 </sst>
 </file>
@@ -899,18 +911,16 @@
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="2" t="str">
-        <f>Classificação!B10</f>
-        <v>Dálmata</v>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="2" t="str">
-        <f>Classificação!B13</f>
-        <v>Onça</v>
+      <c r="G15" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -920,18 +930,16 @@
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="str">
-        <f>Classificação!B11</f>
-        <v>Girafa</v>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="2" t="str">
-        <f>Classificação!B12</f>
-        <v>Tigre</v>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">

--- a/torneio_interno_planilha_preenchivel.xlsx
+++ b/torneio_interno_planilha_preenchivel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B81C87A7-5C75-6446-B183-21C9322E59B3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F173DAF8-45E2-4508-A55D-D0CC5358F1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela de Jogos" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabela de Jogos'!$A$3:$G$13</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
   <si>
     <t>Torneio Interno – Planilha de Jogos</t>
   </si>
@@ -107,6 +107,18 @@
     <t>SEMIFINAIS</t>
   </si>
   <si>
+    <t>1° Lugar</t>
+  </si>
+  <si>
+    <t>4° Lugar</t>
+  </si>
+  <si>
+    <t>2° Lugar</t>
+  </si>
+  <si>
+    <t>3° Lugar</t>
+  </si>
+  <si>
     <t>DISPUTA 3º LUGAR</t>
   </si>
   <si>
@@ -150,18 +162,6 @@
   </si>
   <si>
     <t>Saldo</t>
-  </si>
-  <si>
-    <t>1° Lugar</t>
-  </si>
-  <si>
-    <t>2° Lugar</t>
-  </si>
-  <si>
-    <t>4° Lugar</t>
-  </si>
-  <si>
-    <t>3° Lugar</t>
   </si>
 </sst>
 </file>
@@ -171,7 +171,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,18 +619,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.2265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.97265625" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="11.97265625" customWidth="1"/>
-    <col min="5" max="5" width="7.93359375" customWidth="1"/>
-    <col min="6" max="6" width="11.97265625" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -641,7 +641,7 @@
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="e" cm="1">
@@ -652,7 +652,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -675,7 +675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="27.95" customHeight="1">
       <c r="A4" s="14">
         <v>46248</v>
       </c>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="27.95" customHeight="1">
       <c r="A5" s="14">
         <v>46248</v>
       </c>
@@ -721,7 +721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="27.95" customHeight="1">
       <c r="A6" s="14">
         <v>46255</v>
       </c>
@@ -744,7 +744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="27.95" customHeight="1">
       <c r="A7" s="14">
         <v>46255</v>
       </c>
@@ -767,7 +767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="27.95" customHeight="1">
       <c r="A8" s="14">
         <v>46262</v>
       </c>
@@ -790,7 +790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="27.95" customHeight="1">
       <c r="A9" s="14">
         <v>46262</v>
       </c>
@@ -813,7 +813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="27.95" customHeight="1">
       <c r="A10" s="14">
         <v>46276</v>
       </c>
@@ -836,7 +836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="27.95" customHeight="1">
       <c r="A11" s="14">
         <v>46276</v>
       </c>
@@ -846,16 +846,20 @@
       <c r="C11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
       <c r="G11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="27.95" customHeight="1">
       <c r="A12" s="14">
         <v>46283</v>
       </c>
@@ -874,7 +878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="27.95" customHeight="1">
       <c r="A13" s="14">
         <v>46283</v>
       </c>
@@ -893,7 +897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="17" t="s">
         <v>15</v>
       </c>
@@ -904,7 +908,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
     </row>
-    <row r="15" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="27.95" customHeight="1">
       <c r="A15" s="14">
         <v>46290</v>
       </c>
@@ -912,7 +916,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
@@ -920,10 +924,10 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="27.95" customHeight="1">
       <c r="A16" s="14">
         <v>46290</v>
       </c>
@@ -931,7 +935,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2" t="s">
@@ -939,12 +943,12 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="27.95" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -954,7 +958,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="27.95" customHeight="1">
       <c r="A18" s="14">
         <v>46297</v>
       </c>
@@ -962,7 +966,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="2" t="s">
@@ -970,11 +974,11 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="27.95" customHeight="1">
       <c r="A19" s="14"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -984,9 +988,9 @@
       <c r="G19" s="2"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="27.95" customHeight="1">
       <c r="A20" s="15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -996,7 +1000,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="27.95" customHeight="1">
       <c r="A21" s="14">
         <v>46297</v>
       </c>
@@ -1004,7 +1008,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="2" t="s">
@@ -1012,11 +1016,11 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -1025,7 +1029,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1034,7 +1038,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="B29" s="6"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1043,7 +1047,7 @@
       <c r="G29" s="7"/>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
       <c r="D30" s="8"/>
@@ -1052,7 +1056,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="B31" s="6"/>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
@@ -1061,7 +1065,7 @@
       <c r="G31" s="7"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="B32" s="6"/>
       <c r="C32" s="7"/>
       <c r="D32" s="8"/>
@@ -1070,7 +1074,7 @@
       <c r="G32" s="7"/>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8">
       <c r="B33" s="6"/>
       <c r="C33" s="7"/>
       <c r="D33" s="8"/>
@@ -1079,7 +1083,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8">
       <c r="B34" s="6"/>
       <c r="C34" s="7"/>
       <c r="D34" s="8"/>
@@ -1088,7 +1092,7 @@
       <c r="G34" s="7"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8">
       <c r="B35" s="6"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1097,7 +1101,7 @@
       <c r="G35" s="7"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8">
       <c r="B36" s="6"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -1106,7 +1110,7 @@
       <c r="G36" s="7"/>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8">
       <c r="B37" s="6"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1115,7 +1119,7 @@
       <c r="G37" s="7"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8">
       <c r="B38" s="6"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -1124,7 +1128,7 @@
       <c r="G38" s="7"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8">
       <c r="B39" s="6"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1133,7 +1137,7 @@
       <c r="G39" s="7"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8">
       <c r="B40" s="6"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -1142,7 +1146,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8">
       <c r="B41" s="6"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1151,7 +1155,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8">
       <c r="B42" s="6"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -1160,7 +1164,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8">
       <c r="B43" s="6"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1169,7 +1173,7 @@
       <c r="G43" s="7"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:8">
       <c r="B44" s="6"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -1178,7 +1182,7 @@
       <c r="G44" s="7"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8">
       <c r="B45" s="6"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1187,7 +1191,7 @@
       <c r="G45" s="7"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8">
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -1211,52 +1215,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.93359375" customWidth="1"/>
-    <col min="2" max="2" width="18.0234375" customWidth="1"/>
-    <col min="3" max="3" width="6.05078125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.12890625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.93359375" customWidth="1"/>
-    <col min="6" max="7" width="11.97265625" customWidth="1"/>
-    <col min="8" max="8" width="13.98828125" customWidth="1"/>
-    <col min="9" max="9" width="9.953125" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1297,7 +1301,7 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1337,7 +1341,7 @@
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1350,7 +1354,7 @@
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" ref="D4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" ref="E4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1358,11 +1362,11 @@
       </c>
       <c r="F4" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B4,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B4,'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" ref="G4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H4" s="5" cm="1">
         <f t="array" ref="H4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
@@ -1370,14 +1374,14 @@
       </c>
       <c r="I4" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1386,7 +1390,7 @@
       </c>
       <c r="C5" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B5,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B5,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5" cm="1">
         <f t="array" ref="D5">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B5)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B5)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1394,7 +1398,7 @@
       </c>
       <c r="E5" s="5" cm="1">
         <f t="array" ref="E5">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B5)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B5)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B5,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B5,'Tabela de Jogos'!$F$4:$F$13)</f>
@@ -1406,18 +1410,18 @@
       </c>
       <c r="H5" s="5" cm="1">
         <f t="array" ref="H5">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B5)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B5)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="C6" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B6,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B6,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" cm="1">
         <f t="array" ref="D6">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B6)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B6)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1457,7 +1461,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1472,7 +1476,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1487,82 +1491,82 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="10"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="5">
         <v>1</v>
       </c>
       <c r="B10" s="11" t="str" cm="1">
         <f t="array" ref="B10:I14">_xlfn.SORTBY(B2:I6,F2:F6,-1)</f>
-        <v>Dálmata</v>
+        <v>Tigre</v>
       </c>
       <c r="C10" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>8</v>
+      </c>
+      <c r="G10" s="9">
+        <v>8</v>
+      </c>
+      <c r="H10" s="9">
         <v>1</v>
       </c>
-      <c r="F10" s="9">
-        <v>6</v>
-      </c>
-      <c r="G10" s="9">
-        <v>6</v>
-      </c>
-      <c r="H10" s="9">
-        <v>3</v>
-      </c>
       <c r="I10" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="5">
         <v>2</v>
       </c>
       <c r="B11" s="9" t="str">
-        <v>Girafa</v>
+        <v>Dálmata</v>
       </c>
       <c r="C11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
@@ -1587,40 +1591,40 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="5">
         <v>3</v>
       </c>
       <c r="B12" s="9" t="str">
-        <v>Tigre</v>
+        <v>Girafa</v>
       </c>
       <c r="C12" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="9">
         <v>2</v>
       </c>
       <c r="E12" s="9">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9">
+        <v>6</v>
+      </c>
+      <c r="G12" s="9">
+        <v>6</v>
+      </c>
+      <c r="H12" s="9">
+        <v>6</v>
+      </c>
+      <c r="I12" s="9">
         <v>0</v>
-      </c>
-      <c r="F12" s="9">
-        <v>5</v>
-      </c>
-      <c r="G12" s="9">
-        <v>5</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1</v>
-      </c>
-      <c r="I12" s="9">
-        <v>4</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="5">
         <v>4</v>
       </c>
@@ -1653,7 +1657,7 @@
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14" s="5">
         <v>5</v>
       </c>
@@ -1661,7 +1665,7 @@
         <v>Zebra</v>
       </c>
       <c r="C14" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -1686,7 +1690,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1701,7 +1705,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>

--- a/torneio_interno_planilha_preenchivel.xlsx
+++ b/torneio_interno_planilha_preenchivel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F173DAF8-45E2-4508-A55D-D0CC5358F1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7F61CF-A96D-0244-BCD7-61EE92977D28}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela de Jogos" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabela de Jogos'!$A$3:$G$13</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -107,61 +107,61 @@
     <t>SEMIFINAIS</t>
   </si>
   <si>
+    <t>DISPUTA 3º LUGAR</t>
+  </si>
+  <si>
+    <t>Perdedor Semi 1</t>
+  </si>
+  <si>
+    <t>Perdedor Semi 2</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>Vencedor Semi 1</t>
+  </si>
+  <si>
+    <t>Vencedor Semi 2</t>
+  </si>
+  <si>
+    <t>Pos.</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Jogos</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Derrota</t>
+  </si>
+  <si>
+    <t>Pontos</t>
+  </si>
+  <si>
+    <t>Sets Pró</t>
+  </si>
+  <si>
+    <t>Sets Contra</t>
+  </si>
+  <si>
+    <t>Saldo</t>
+  </si>
+  <si>
     <t>1° Lugar</t>
   </si>
   <si>
+    <t>2° Lugar</t>
+  </si>
+  <si>
     <t>4° Lugar</t>
   </si>
   <si>
-    <t>2° Lugar</t>
-  </si>
-  <si>
     <t>3° Lugar</t>
-  </si>
-  <si>
-    <t>DISPUTA 3º LUGAR</t>
-  </si>
-  <si>
-    <t>Perdedor Semi 1</t>
-  </si>
-  <si>
-    <t>Perdedor Semi 2</t>
-  </si>
-  <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>Vencedor Semi 1</t>
-  </si>
-  <si>
-    <t>Vencedor Semi 2</t>
-  </si>
-  <si>
-    <t>Pos.</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Jogos</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Derrota</t>
-  </si>
-  <si>
-    <t>Pontos</t>
-  </si>
-  <si>
-    <t>Sets Pró</t>
-  </si>
-  <si>
-    <t>Sets Contra</t>
-  </si>
-  <si>
-    <t>Saldo</t>
   </si>
 </sst>
 </file>
@@ -171,7 +171,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,18 +619,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="33.2265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.97265625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11.97265625" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" customWidth="1"/>
+    <col min="6" max="6" width="11.97265625" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -641,7 +641,7 @@
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="e" cm="1">
@@ -652,7 +652,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1">
+    <row r="3" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -675,7 +675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.95" customHeight="1">
+    <row r="4" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46248</v>
       </c>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.95" customHeight="1">
+    <row r="5" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14">
         <v>46248</v>
       </c>
@@ -721,7 +721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.95" customHeight="1">
+    <row r="6" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14">
         <v>46255</v>
       </c>
@@ -744,7 +744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.95" customHeight="1">
+    <row r="7" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14">
         <v>46255</v>
       </c>
@@ -767,7 +767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.95" customHeight="1">
+    <row r="8" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>46262</v>
       </c>
@@ -790,7 +790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.95" customHeight="1">
+    <row r="9" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14">
         <v>46262</v>
       </c>
@@ -813,7 +813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.95" customHeight="1">
+    <row r="10" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>46276</v>
       </c>
@@ -836,7 +836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.95" customHeight="1">
+    <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14">
         <v>46276</v>
       </c>
@@ -859,7 +859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.95" customHeight="1">
+    <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>46283</v>
       </c>
@@ -869,16 +869,20 @@
       <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3">
+        <v>3</v>
+      </c>
       <c r="G12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.95" customHeight="1">
+    <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14">
         <v>46283</v>
       </c>
@@ -897,7 +901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.95" customHeight="1">
+    <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>15</v>
       </c>
@@ -908,7 +912,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
     </row>
-    <row r="15" spans="1:7" ht="27.95" customHeight="1">
+    <row r="15" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14">
         <v>46290</v>
       </c>
@@ -916,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
@@ -924,10 +928,10 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.95" customHeight="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <v>46290</v>
       </c>
@@ -935,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2" t="s">
@@ -943,12 +947,12 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="27.95" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -958,7 +962,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="27.95" customHeight="1">
+    <row r="18" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>46297</v>
       </c>
@@ -966,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="2" t="s">
@@ -974,11 +978,11 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="27.95" customHeight="1">
+    <row r="19" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -988,9 +992,9 @@
       <c r="G19" s="2"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="27.95" customHeight="1">
+    <row r="20" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -1000,7 +1004,7 @@
       <c r="G20" s="16"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="27.95" customHeight="1">
+    <row r="21" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="14">
         <v>46297</v>
       </c>
@@ -1008,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="2" t="s">
@@ -1016,11 +1020,11 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -1029,7 +1033,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1038,7 +1042,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="6"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1047,7 +1051,7 @@
       <c r="G29" s="7"/>
       <c r="H29" s="6"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
       <c r="D30" s="8"/>
@@ -1056,7 +1060,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="6"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B31" s="6"/>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
@@ -1065,7 +1069,7 @@
       <c r="G31" s="7"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B32" s="6"/>
       <c r="C32" s="7"/>
       <c r="D32" s="8"/>
@@ -1074,7 +1078,7 @@
       <c r="G32" s="7"/>
       <c r="H32" s="6"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="6"/>
       <c r="C33" s="7"/>
       <c r="D33" s="8"/>
@@ -1083,7 +1087,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="6"/>
       <c r="C34" s="7"/>
       <c r="D34" s="8"/>
@@ -1092,7 +1096,7 @@
       <c r="G34" s="7"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="6"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1101,7 +1105,7 @@
       <c r="G35" s="7"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="6"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -1110,7 +1114,7 @@
       <c r="G36" s="7"/>
       <c r="H36" s="6"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="6"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1119,7 +1123,7 @@
       <c r="G37" s="7"/>
       <c r="H37" s="6"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="6"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -1128,7 +1132,7 @@
       <c r="G38" s="7"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="6"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1137,7 +1141,7 @@
       <c r="G39" s="7"/>
       <c r="H39" s="6"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="6"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -1146,7 +1150,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="6"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="6"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1155,7 +1159,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="6"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -1164,7 +1168,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="6"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1173,7 +1177,7 @@
       <c r="G43" s="7"/>
       <c r="H43" s="6"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="6"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -1182,7 +1186,7 @@
       <c r="G44" s="7"/>
       <c r="H44" s="6"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="6"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1191,7 +1195,7 @@
       <c r="G45" s="7"/>
       <c r="H45" s="6"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -1215,52 +1219,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="1" max="1" width="7.93359375" customWidth="1"/>
+    <col min="2" max="2" width="18.0234375" customWidth="1"/>
+    <col min="3" max="3" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.12890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.93359375" customWidth="1"/>
+    <col min="6" max="7" width="11.97265625" customWidth="1"/>
+    <col min="8" max="8" width="13.98828125" customWidth="1"/>
+    <col min="9" max="9" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1301,7 +1305,7 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="C3" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B3,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B3,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5" cm="1">
         <f t="array" ref="D3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1318,7 +1322,7 @@
       </c>
       <c r="E3" s="5" cm="1">
         <f t="array" ref="E3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B3,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B3,'Tabela de Jogos'!$F$4:$F$13)</f>
@@ -1330,18 +1334,18 @@
       </c>
       <c r="H3" s="5" cm="1">
         <f t="array" ref="H3">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B3)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B3)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I6" si="0">G3-H3</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1350,7 +1354,7 @@
       </c>
       <c r="C4" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B4,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B4,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" ref="D4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1381,7 +1385,7 @@
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1421,7 +1425,7 @@
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1434,7 +1438,7 @@
       </c>
       <c r="D6" s="5" cm="1">
         <f t="array" ref="D6">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B6)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B6)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5" cm="1">
         <f t="array" ref="E6">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B6)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B6)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1442,11 +1446,11 @@
       </c>
       <c r="F6" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B6,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B6,'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="5" cm="1">
         <f t="array" ref="G6">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B6)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B6)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6" s="5" cm="1">
         <f t="array" ref="H6">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B6)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B6)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
@@ -1454,14 +1458,14 @@
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1476,7 +1480,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1491,40 +1495,40 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="10"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>1</v>
       </c>
@@ -1533,7 +1537,7 @@
         <v>Tigre</v>
       </c>
       <c r="C10" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -1558,7 +1562,7 @@
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>2</v>
       </c>
@@ -1591,7 +1595,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>3</v>
       </c>
@@ -1624,73 +1628,73 @@
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>4</v>
       </c>
       <c r="B13" s="9" t="str">
-        <v>Onça</v>
+        <v>Zebra</v>
       </c>
       <c r="C13" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I13" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>5</v>
       </c>
       <c r="B14" s="9" t="str">
-        <v>Zebra</v>
+        <v>Onça</v>
       </c>
       <c r="C14" s="9">
         <v>4</v>
       </c>
       <c r="D14" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="9">
         <v>3</v>
       </c>
       <c r="F14" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="9">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1705,7 +1709,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>

--- a/torneio_interno_planilha_preenchivel.xlsx
+++ b/torneio_interno_planilha_preenchivel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="148" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7F61CF-A96D-0244-BCD7-61EE92977D28}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{22D47F29-216A-474A-81B3-552C820083B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AEC95D8-610F-304E-A069-8740807FF892}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
   <si>
     <t>Torneio Interno – Planilha de Jogos</t>
   </si>
@@ -150,18 +150,6 @@
   </si>
   <si>
     <t>Saldo</t>
-  </si>
-  <si>
-    <t>1° Lugar</t>
-  </si>
-  <si>
-    <t>2° Lugar</t>
-  </si>
-  <si>
-    <t>4° Lugar</t>
-  </si>
-  <si>
-    <t>3° Lugar</t>
   </si>
 </sst>
 </file>
@@ -892,11 +880,15 @@
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
       </c>
@@ -919,16 +911,18 @@
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>31</v>
+      <c r="C15" s="2" t="str">
+        <f>Classificação!B10</f>
+        <v>Tigre</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="2" t="s">
-        <v>33</v>
+      <c r="G15" s="2" t="str">
+        <f>Classificação!B13</f>
+        <v>Zebra</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -938,16 +932,18 @@
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>32</v>
+      <c r="C16" s="2" t="str">
+        <f>Classificação!B11</f>
+        <v>Dálmata</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="2" t="s">
-        <v>34</v>
+      <c r="G16" s="2" t="str">
+        <f>Classificação!B12</f>
+        <v>Girafa</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1274,11 +1270,11 @@
       </c>
       <c r="C2" s="5">
         <f>COUNTIFS('Tabela de Jogos'!$C$4:$C$13,B2,'Tabela de Jogos'!$D$4:$D$13,"&lt;&gt;") + COUNTIFS('Tabela de Jogos'!$G$5:$G$14,B2,'Tabela de Jogos'!$F$4:$F$13,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="5" cm="1">
         <f t="array" ref="D2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&gt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&gt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="5" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
@@ -1286,19 +1282,19 @@
       </c>
       <c r="F2" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B2,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B2,'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2" s="5" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" s="5" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B2)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B2)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="5">
         <f>G2-H2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -1362,23 +1358,23 @@
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" ref="E4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&lt;'Tabela de Jogos'!$F$4:$F$13))+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&lt;'Tabela de Jogos'!$D$4:$D$13))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5">
         <f>SUMIF('Tabela de Jogos'!$C$4:$C$13,B4,'Tabela de Jogos'!$D$4:$D$13) + SUMIF('Tabela de Jogos'!$G$4:$G$13,B4,'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" ref="G4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" cm="1">
         <f t="array" ref="H4">SUMPRODUCT(('Tabela de Jogos'!$C$4:$C$13=B4)*('Tabela de Jogos'!$D$4:$D$13&lt;&gt;"")*'Tabela de Jogos'!$F$4:$F$13)+SUMPRODUCT(('Tabela de Jogos'!$G$4:$G$13=B4)*('Tabela de Jogos'!$F$4:$F$13&lt;&gt;"")*'Tabela de Jogos'!$D$4:$D$13)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -1543,19 +1539,19 @@
         <v>3</v>
       </c>
       <c r="E10" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -1570,25 +1566,25 @@
         <v>Dálmata</v>
       </c>
       <c r="C11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9">
         <v>1</v>
       </c>
       <c r="F11" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
